--- a/all_sim/det_gpt_realset.xlsx
+++ b/all_sim/det_gpt_realset.xlsx
@@ -335,7 +335,7 @@
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.7383333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.1259259259259259</v>
+        <v>0.5137826350941105</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.09444444444444444</v>
+        <v>0.4996031746031746</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.20833333333333334</v>
+        <v>0.4825450450450451</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.20833333333333334</v>
+        <v>0.4825450450450451</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.225</v>
+        <v>0.4908783783783784</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.2642857142857143</v>
+        <v>0.5295787545787546</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.2642857142857143</v>
+        <v>0.5295787545787546</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.2642857142857143</v>
+        <v>0.5589721254355401</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.34285714285714286</v>
+        <v>0.5825396825396825</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.34285714285714286</v>
+        <v>0.5825396825396825</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.34285714285714286</v>
+        <v>0.5489795918367346</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.075</v>
+        <v>0.3859848484848485</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.44696969696969696</v>
+        <v>0.6800065876152833</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.8111111111111112</v>
+        <v>0.8631826741996234</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.67989417989418</v>
+        <v>0.7975742085911578</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.67989417989418</v>
+        <v>0.7975742085911578</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.31379731379731385</v>
+        <v>0.6061740192174975</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.030893477182539684</v>
+        <v>0.3247992565768813</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7455128205128206</v>
+        <v>0.8102564102564103</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.6494755244755246</v>
+        <v>0.7643929346515554</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.6494755244755246</v>
+        <v>0.7643929346515554</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.6131656804733727</v>
+        <v>0.7462380126504795</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.6372377622377623</v>
+        <v>0.7582740535326742</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.4758297258297259</v>
+        <v>0.7217858306567985</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.5415812257917522</v>
+        <v>0.7253360674413306</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.46320346320346323</v>
+        <v>0.7003517316017316</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.45539096320346323</v>
+        <v>0.6651954816017316</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.45539096320346323</v>
+        <v>0.6651954816017316</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.5505724538619274</v>
+        <v>0.699528651173388</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.4300899621212122</v>
+        <v>0.6525449810606061</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.4300899621212122</v>
+        <v>0.6525449810606061</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.4300899621212122</v>
+        <v>0.6525449810606061</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.4300899621212122</v>
+        <v>0.6525449810606061</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.5777777777777778</v>
+        <v>0.7483483483483484</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.7047619047619047</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.3678571428571429</v>
+        <v>0.6312969924812031</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.3678571428571429</v>
+        <v>0.6163610038610039</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.7011204481792717</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.6076388888888888</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.6076388888888888</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.2569444444444444</v>
+        <v>0.6046626984126984</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.41071428571428575</v>
+        <v>0.6957417582417582</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.5831845238095237</v>
+        <v>0.7915922619047618</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6816374663072776</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6816374663072776</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6816374663072776</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6553571428571429</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6816374663072776</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6816374663072776</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.225</v>
+        <v>0.6030660377358491</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.15833333333333335</v>
+        <v>0.5599358974358974</v>
       </c>
     </row>
     <row r="11">
@@ -726,28 +726,28 @@
         <v>1.0</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.6277709359605912</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.03900266400266399</v>
+        <v>0.433563832001332</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.04779040404040404</v>
+        <v>0.4405618686868687</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.24787878787878787</v>
+        <v>0.5406060606060606</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.07998028756957329</v>
+        <v>0.45405264378478666</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.07998028756957329</v>
+        <v>0.45405264378478666</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.07998028756957329</v>
+        <v>0.45405264378478666</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.06998275162337662</v>
+        <v>0.4490538758116883</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.09294871794871797</v>
+        <v>0.45951783723522854</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.8502164502164503</v>
+        <v>0.9251082251082252</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.4675324675324675</v>
+        <v>0.7018513401492125</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.6948611111111112</v>
+        <v>0.8474305555555556</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.6948611111111112</v>
+        <v>0.8474305555555556</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5148611111111114</v>
+        <v>0.7505812404870625</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.6948611111111112</v>
+        <v>0.8474305555555556</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.6948611111111112</v>
+        <v>0.8474305555555556</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.6948611111111112</v>
+        <v>0.8474305555555556</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.45708333333333345</v>
+        <v>0.7150281531531533</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.45708333333333345</v>
+        <v>0.7022258771929826</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.45708333333333345</v>
+        <v>0.7216923515981736</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.45708333333333345</v>
+        <v>0.7216923515981736</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9565934065934066</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.7089898053753476</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.2254251700680272</v>
+        <v>0.5146733693477391</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.2254251700680272</v>
+        <v>0.5146733693477391</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.16301020408163266</v>
+        <v>0.5030737294917967</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.6942857142857142</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5897435897435898</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.5486111111111112</v>
+        <v>0.7460036687631028</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.5486111111111112</v>
+        <v>0.7641014739229025</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.4236111111111111</v>
+        <v>0.6909722222222222</v>
       </c>
     </row>
     <row r="18">

--- a/all_sim/det_gpt_realset.xlsx
+++ b/all_sim/det_gpt_realset.xlsx
@@ -340,7 +340,7 @@
     <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.5137826350941105</v>
+        <v>0.11353976927747418</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.4996031746031746</v>
+        <v>0.08544973544973544</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.4825450450450451</v>
+        <v>0.15765765765765768</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.4825450450450451</v>
+        <v>0.15765765765765768</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.4908783783783784</v>
+        <v>0.17027027027027028</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.5295787545787546</v>
+        <v>0.2100732600732601</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.5295787545787546</v>
+        <v>0.2100732600732601</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.5589721254355401</v>
+        <v>0.22560975609756098</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.5825396825396825</v>
+        <v>0.2819047619047619</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.5825396825396825</v>
+        <v>0.2819047619047619</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.5489795918367346</v>
+        <v>0.2588921282798834</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.3859848484848485</v>
+        <v>0.052272727272727276</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.6800065876152833</v>
+        <v>0.408102766798419</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.8631826741996234</v>
+        <v>0.7423728813559323</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.7975742085911578</v>
+        <v>0.6222760290556901</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.7975742085911578</v>
+        <v>0.6222760290556901</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.6061740192174975</v>
+        <v>0.28196280370193416</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.3247992565768813</v>
+        <v>0.01911394991149937</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.8102564102564103</v>
+        <v>0.652323717948718</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.7643929346515554</v>
+        <v>0.571090547383651</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.7643929346515554</v>
+        <v>0.571090547383651</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.7462380126504795</v>
+        <v>0.5391629259334829</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.7582740535326742</v>
+        <v>0.5603297564504461</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.7217858306567985</v>
+        <v>0.4604803798352186</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.7253360674413306</v>
+        <v>0.49234656890159284</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.7003517316017316</v>
+        <v>0.4342532467532468</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.6651954816017316</v>
+        <v>0.39846709280303033</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.6651954816017316</v>
+        <v>0.39846709280303033</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.699528651173388</v>
+        <v>0.46715238509496876</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.6525449810606061</v>
+        <v>0.3763287168560607</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.6525449810606061</v>
+        <v>0.3763287168560607</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.6525449810606061</v>
+        <v>0.3763287168560607</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.6525449810606061</v>
+        <v>0.3763287168560607</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.7483483483483484</v>
+        <v>0.5309309309309309</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.7047619047619047</v>
+        <v>0.44</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.6312969924812031</v>
+        <v>0.32913533834586467</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.6163610038610039</v>
+        <v>0.3181467181467182</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.7011204481792717</v>
+        <v>0.44719887955182075</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.5738811728395061</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.7760416666666666</v>
+        <v>0.5738811728395061</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.6046626984126984</v>
+        <v>0.24470899470899468</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.6957417582417582</v>
+        <v>0.4028159340659341</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.7915922619047618</v>
+        <v>0.5831845238095237</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.6816374663072776</v>
+        <v>0.37493261455525606</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.6816374663072776</v>
+        <v>0.37493261455525606</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.6816374663072776</v>
+        <v>0.37493261455525606</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.6553571428571429</v>
+        <v>0.3548469387755102</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.6816374663072776</v>
+        <v>0.37493261455525606</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.6816374663072776</v>
+        <v>0.37493261455525606</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.6030660377358491</v>
+        <v>0.22075471698113208</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.5599358974358974</v>
+        <v>0.15224358974358976</v>
       </c>
     </row>
     <row r="11">
@@ -726,28 +726,28 @@
         <v>1.0</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.6277709359605912</v>
+        <v>0.3140394088669951</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.433563832001332</v>
+        <v>0.03229908112720612</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.4405618686868687</v>
+        <v>0.0398253367003367</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.5406060606060606</v>
+        <v>0.20656565656565656</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.45405264378478666</v>
+        <v>0.06623367564355288</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.45405264378478666</v>
+        <v>0.06623367564355288</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.45405264378478666</v>
+        <v>0.06623367564355288</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.4490538758116883</v>
+        <v>0.05795446618810877</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.45951783723522854</v>
+        <v>0.07678372352285397</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.9251082251082252</v>
+        <v>0.8502164502164503</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.7018513401492125</v>
+        <v>0.4376899696048632</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.8474305555555556</v>
+        <v>0.6948611111111112</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.8474305555555556</v>
+        <v>0.6948611111111112</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.7505812404870625</v>
+        <v>0.5078082191780825</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.8474305555555556</v>
+        <v>0.6948611111111112</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.8474305555555556</v>
+        <v>0.6948611111111112</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.8474305555555556</v>
+        <v>0.6948611111111112</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.7150281531531533</v>
+        <v>0.44472972972972985</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.7022258771929826</v>
+        <v>0.4330263157894738</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.7216923515981736</v>
+        <v>0.4508219178082193</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.7216923515981736</v>
+        <v>0.4508219178082193</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.9565934065934066</v>
+        <v>0.9142857142857144</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.7089898053753476</v>
+        <v>0.4735866543095459</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5146733693477391</v>
+        <v>0.18122415632919836</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.5146733693477391</v>
+        <v>0.18122415632919836</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.5030737294917967</v>
+        <v>0.13743997599039617</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.6942857142857142</v>
+        <v>0.4639999999999999</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.28205128205128205</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.7460036687631028</v>
+        <v>0.5175576519916143</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.7641014739229025</v>
+        <v>0.5374149659863946</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.6909722222222222</v>
+        <v>0.40596064814814814</v>
       </c>
     </row>
     <row r="18">
